--- a/GameData/DataTables/Board/LevelTable.xlsx
+++ b/GameData/DataTables/Board/LevelTable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,22 +445,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>RoundCount</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TargetScore</t>
+          <t>InitialPartCount</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>InitialArmMoves</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>InitialPublicRepairEnergy</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Objective</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>EventKey</t>
         </is>
       </c>
     </row>
@@ -482,17 +507,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -504,27 +554,377 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>维修关卡的骨架定义</t>
+          <t>维修关卡的基础定义</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>关卡稳定键</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>关卡显示名称</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>盘面半径档位 n，合法格数 3n(n-1)+1</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>本关轮数</t>
+          <t>盘面半径档位 n</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>本关目标分数</t>
+          <t>初盘零件总数</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>初始机械臂次数</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>初始公共维修能量</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>关卡目标文案</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>预计耗时格数</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>绑定事件稳定键</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EV-N01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>卡住的卷帘门</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>把门轴联系标记推入校正格，让卷帘门重新卡回轨道</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>EV-N01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>T-G01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>贯通撞锤试机</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>输出侧推移到位</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>T-G02</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>横推撞锤试机</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>同次双路推动</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>T-G03</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>轴向线圈试机</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>射线越过空格命中端点</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>T-G04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>定时线圈试机</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>待爆后搬位并在下一拍命中端点</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TUT-RC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>旋转与碰撞</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>来撞件沿重力撞上撞锤</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TUT-ER</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>能量与维修</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>棘轮产出公共维修能量并完成维修</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TUT-BC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>爆破与拆障</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>爆破线圈起爆并冲击邻件</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>REDSHOE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>停不下来的排练</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>导流→与沈遥分离→维修封存匣→封存红鞋</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>L-01-01</t>
         </is>
       </c>
     </row>
